--- a/data/bom.xlsx
+++ b/data/bom.xlsx
@@ -2107,7 +2107,7 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="113">
@@ -2122,7 +2122,7 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="114">
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="115">
@@ -2152,7 +2152,7 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="116">
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="117">
@@ -2182,7 +2182,7 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="118">
@@ -2197,7 +2197,7 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="119">
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="120">
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="121">
@@ -2242,7 +2242,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="122">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="123">
@@ -2272,7 +2272,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="124">
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="125">
@@ -2302,7 +2302,7 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="126">
@@ -2317,7 +2317,7 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="127">
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="128">
@@ -2347,7 +2347,7 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="129">
@@ -2362,7 +2362,7 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="130">
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="131">
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="132">
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="133">
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="134">
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="135">
@@ -2452,7 +2452,7 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="136">
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="137">
@@ -2482,7 +2482,7 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="138">
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="139">
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="140">
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="141">
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="142">
@@ -2557,7 +2557,7 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="143">
@@ -2572,7 +2572,7 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="144">
@@ -2587,7 +2587,7 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="145">
@@ -2602,7 +2602,7 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="146">
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="147">
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="148">
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="149">
@@ -2662,7 +2662,7 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="150">
@@ -2677,7 +2677,7 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="151">
@@ -2692,7 +2692,7 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="152">
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="153">
@@ -2722,7 +2722,7 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="154">
@@ -2737,7 +2737,7 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="155">
@@ -2752,7 +2752,7 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="156">
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
